--- a/ejemplos/Importar-correctos.xlsx
+++ b/ejemplos/Importar-correctos.xlsx
@@ -457,7 +457,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Código externo</t>
+          <t>Código proveedor</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
